--- a/hira_material_automation/output/monthly/202601_202606__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__nonmetal_anchor__040019__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:23:56</t>
+          <t>2026-06-14T22:17:16</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b0081e3bd6251bd670a7b3176a3d4040635b861a3de069630a91c57263a93886</t>
+          <t>c5140bda8e1a4a039dca0cae6fef86fdca666099a16ba5e1203e24bd8983204f</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__nonmetal_anchor__040019__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:17:16</t>
+          <t>2026-06-24T22:22:02</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c5140bda8e1a4a039dca0cae6fef86fdca666099a16ba5e1203e24bd8983204f</t>
+          <t>18c6a8b38f6039610c2cbd43b1cdaf0bda9b1e77a4f98331af09b490d559d608</t>
         </is>
       </c>
     </row>
